--- a/Seguimiento submissions.xlsx
+++ b/Seguimiento submissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luiyi\Dropbox\Lu\Backup\Big data y Machine Learning para Economía Aplicada\Taller-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF6AD2F-671A-4FA2-9BD7-D8FFD6C16CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE26EE37-B2BF-4BC3-8ACB-71D448065923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{61DA3C93-0847-4C6B-9B33-18547C96FEBD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t xml:space="preserve">Archivo </t>
   </si>
@@ -81,6 +81,36 @@
   </si>
   <si>
     <t xml:space="preserve">Hay una diferencia abislmal entre el error de train y el de generalización. Además, el error de generalización es altísimo, teniendo en cuenta que el promedio de los precios de las propiedades es de 654.534.675. Creo que tiene que ver con la cantidad de observaciones usadas. Se usaron para entrenar, 4.307 observaciones y se evaluó en 10.286. Creo que es mejor tratar primero los NAs y después si reestimar el modelo a ver qué pasa. </t>
+  </si>
+  <si>
+    <t>xgboost11</t>
+  </si>
+  <si>
+    <t>eta = 0.05
+max_depth = 8
+gamma = 0.1
+colsample_bytree = 0.75
+min_child_weight = 20
+subsample = 0.75
+nrounds = 1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En esta iteración se buscó en la variable de texto para completar los NAs de área total, construída, baños y cuartos, lo cual disminuyó un tercio los NAs, igual quedan todavía NAs. Además, se crearon variables que contaba los NAs de estas variables para permitirle al xgboost aprender de los missings. Por último, se sacó el logaritmo de los precios. Se puede ver que el error de validación disminuyó, pero el error del train aumentó, lo que podría indicar sobreajuste. También se oberva que, igual que en el caso anterior, la brecha entre el error de validación y de entrenamiento es alta. Lo que puede indicar que las propiedades de chapinero no tienen características silimilares al resto de barrios de Bogotá. </t>
+  </si>
+  <si>
+    <t>xgboost_spatial_cv</t>
+  </si>
+  <si>
+    <t>Todas + lat y lon + estrato</t>
+  </si>
+  <si>
+    <t>eta = 0.05
+max_depth = 8
+gamma = 0.1
+colsample_bytree = 0.75
+min_child_weight = 20
+subsample = 0.75
+nrounds = 500</t>
   </si>
 </sst>
 </file>
@@ -129,7 +159,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -146,6 +176,12 @@
     </xf>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -482,12 +518,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70B91BE-477A-4823-BA77-A1BE7105F8DB}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="3" max="3" width="13.81640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.453125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="86.08984375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -498,7 +534,7 @@
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
@@ -521,7 +557,7 @@
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -535,6 +571,49 @@
       </c>
       <c r="G2" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="4">
+        <v>112305618</v>
+      </c>
+      <c r="F3" s="4">
+        <v>251808804.86000001</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="1" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="4">
+        <v>135434740</v>
+      </c>
+      <c r="F4" s="4">
+        <v>183644146</v>
       </c>
     </row>
   </sheetData>

--- a/Seguimiento submissions.xlsx
+++ b/Seguimiento submissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luiyi\Dropbox\Lu\Backup\Big data y Machine Learning para Economía Aplicada\Taller-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE26EE37-B2BF-4BC3-8ACB-71D448065923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F161CB05-F608-4122-8B3E-53ACACA2F01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{61DA3C93-0847-4C6B-9B33-18547C96FEBD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t xml:space="preserve">Archivo </t>
   </si>
@@ -111,6 +111,35 @@
 min_child_weight = 20
 subsample = 0.75
 nrounds = 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se redujo el error de validación y se redujo también la brecha entre el error de train y el de validación. </t>
+  </si>
+  <si>
+    <t>xgboost_spatial_cv2</t>
+  </si>
+  <si>
+    <t>Todas - lat y lon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sin las variables de lat y lon el error de validación aumentó. </t>
+  </si>
+  <si>
+    <t>NN_rmsprop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Neyronal </t>
+  </si>
+  <si>
+    <t>L1: units = 128, activation = relu
+L2: rate = 0.20
+L3: units = 64, activation = relu
+L4: rate = 0.20
+L5: units = 32, activation = relu
+L6: units = 1, activation = linear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No es una mejora con respecto al mejor xgboost. Además, hay una brecha amplia entre train y valid. </t>
   </si>
 </sst>
 </file>
@@ -159,7 +188,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -182,6 +211,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -518,11 +556,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70B91BE-477A-4823-BA77-A1BE7105F8DB}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="17.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.08984375" customWidth="1"/>
     <col min="5" max="6" width="13.453125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="86.08984375" customWidth="1"/>
   </cols>
@@ -615,6 +654,55 @@
       <c r="F4" s="4">
         <v>183644146</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="9" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="11">
+        <v>135434740</v>
+      </c>
+      <c r="F5" s="11">
+        <v>249413067.63999999</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="9" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="11">
+        <v>122142601</v>
+      </c>
+      <c r="F6" s="11">
+        <v>237152443.13</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Seguimiento submissions.xlsx
+++ b/Seguimiento submissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luiyi\Dropbox\Lu\Backup\Big data y Machine Learning para Economía Aplicada\Taller-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F161CB05-F608-4122-8B3E-53ACACA2F01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F165C59F-8C70-4A0E-A821-CF0ACED40EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{61DA3C93-0847-4C6B-9B33-18547C96FEBD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t xml:space="preserve">Archivo </t>
   </si>
@@ -128,7 +128,10 @@
     <t>NN_rmsprop</t>
   </si>
   <si>
-    <t xml:space="preserve">Red Neyronal </t>
+    <t xml:space="preserve">No es una mejora con respecto al mejor xgboost. Además, hay una brecha amplia entre train y valid. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red Neuronal </t>
   </si>
   <si>
     <t>L1: units = 128, activation = relu
@@ -136,10 +139,40 @@
 L3: units = 64, activation = relu
 L4: rate = 0.20
 L5: units = 32, activation = relu
-L6: units = 1, activation = linear</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No es una mejora con respecto al mejor xgboost. Además, hay una brecha amplia entre train y valid. </t>
+L6: units = 1, activation = linear
+epochs = 500
+batch_size = 64</t>
+  </si>
+  <si>
+    <t>L1: units = 64, activation = relu, regularizer = 0.001
+L2: units = 32, activation = relu, regularizer = 0.001
+L3: units = 1, activation = linear
+early_stopping = 30
+epochs = 500
+batch_size = 64</t>
+  </si>
+  <si>
+    <t>NN_rmsprop2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No es una mejora con respecto a la primer NN. </t>
+  </si>
+  <si>
+    <t>Red Neuronal + regularización</t>
+  </si>
+  <si>
+    <t>NN_rmsprop3</t>
+  </si>
+  <si>
+    <t>Red Neuronal + simple</t>
+  </si>
+  <si>
+    <t>L1: units = 64, activation = relu
+L2: units = 32, activation = relu
+L3: units = 1, activation = linear
+early_stopping = 30
+epochs = 500
+batch_size = 64</t>
   </si>
 </sst>
 </file>
@@ -556,13 +589,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70B91BE-477A-4823-BA77-A1BE7105F8DB}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.81640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.08984375" customWidth="1"/>
-    <col min="5" max="6" width="13.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="86.08984375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -681,18 +715,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="9" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" s="9" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="11">
         <v>122142601</v>
@@ -701,7 +735,50 @@
         <v>237152443.13</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="1" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4">
+        <v>142369043</v>
+      </c>
+      <c r="F7" s="4">
+        <v>262782527.15000001</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="1" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4">
+        <v>129073151</v>
+      </c>
+      <c r="F8" s="4">
+        <v>238568458.66</v>
       </c>
     </row>
   </sheetData>

--- a/Seguimiento submissions.xlsx
+++ b/Seguimiento submissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luiyi\Dropbox\Lu\Backup\Big data y Machine Learning para Economía Aplicada\Taller-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F165C59F-8C70-4A0E-A821-CF0ACED40EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45CF8A1-6B74-486F-B822-9AA78E6524E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{61DA3C93-0847-4C6B-9B33-18547C96FEBD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t xml:space="preserve">Archivo </t>
   </si>
@@ -173,6 +173,21 @@
 early_stopping = 30
 epochs = 500
 batch_size = 64</t>
+  </si>
+  <si>
+    <t>xgboost_spatial_cv_dtm</t>
+  </si>
+  <si>
+    <t>Todas + lat y lon + estrato + dtm (8978 col)</t>
+  </si>
+  <si>
+    <t>eta = 0.05
+max_depth = 8
+gamma = 0
+colsample_bytree = 0.66
+min_child_weight = 20
+subsample = 0.66
+nrounds = 1000</t>
   </si>
 </sst>
 </file>
@@ -589,10 +604,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70B91BE-477A-4823-BA77-A1BE7105F8DB}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.81640625" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.08984375" customWidth="1"/>
@@ -715,69 +730,89 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="9" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" s="9" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="11">
+        <v>124554398</v>
+      </c>
+      <c r="F6" s="11">
+        <v>175637962.86000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="9" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E7" s="11">
         <v>122142601</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F7" s="11">
         <v>237152443.13</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="116" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:7" s="1" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="4">
-        <v>142369043</v>
-      </c>
-      <c r="F7" s="4">
-        <v>262782527.15000001</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="4">
+        <v>142369043</v>
+      </c>
+      <c r="F8" s="4">
+        <v>262782527.15000001</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="1" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E9" s="4">
         <v>129073151</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F9" s="4">
         <v>238568458.66</v>
       </c>
     </row>

--- a/Seguimiento submissions.xlsx
+++ b/Seguimiento submissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luiyi\Dropbox\Lu\Backup\Big data y Machine Learning para Economía Aplicada\Taller-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45CF8A1-6B74-486F-B822-9AA78E6524E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A45A775-B950-4B79-8080-E384554558F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{61DA3C93-0847-4C6B-9B33-18547C96FEBD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t xml:space="preserve">Archivo </t>
   </si>
@@ -188,6 +188,43 @@
 min_child_weight = 20
 subsample = 0.66
 nrounds = 1000</t>
+  </si>
+  <si>
+    <t>xboost_spatial_cv_dtm2</t>
+  </si>
+  <si>
+    <t>xboost_spatial_cv_dtm3</t>
+  </si>
+  <si>
+    <t>eta = 0.05
+max_depth = 8
+gamma = 0.01
+colsample_bytree = 0.66
+min_child_weight = 20
+subsample = 0.66
+nrounds = 1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colocar una mayor cantidad de documentos que contengan términos frecuentes mejoró el error fuera de muestra. </t>
+  </si>
+  <si>
+    <t>objective = reg_absoluteerror
+eta = 0.05
+max_depth = 8
+gamma = 0.001
+colsample_bytree = 0.75
+min_child_weight = 40
+subsample = 0.66
+nrounds = 1000</t>
+  </si>
+  <si>
+    <t>Usar como función objetivo el MAE empeora la predicción con respecto al SME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hay muchas columnas hay que ver cómo bajar la dimensionalidad. </t>
+  </si>
+  <si>
+    <t>Todas + lat y lon + estrato + dtm (889 col)</t>
   </si>
 </sst>
 </file>
@@ -604,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70B91BE-477A-4823-BA77-A1BE7105F8DB}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
@@ -749,70 +786,119 @@
       <c r="F6" s="11">
         <v>175637962.86000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" s="9" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="G6" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="9" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="11">
+        <v>124881898</v>
+      </c>
+      <c r="F7" s="11">
+        <v>175322522.63999999</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="9" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="11">
+        <v>128582871</v>
+      </c>
+      <c r="F8" s="11">
+        <v>192183645.11000001</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="9" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="A9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E9" s="11">
         <v>122142601</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F9" s="11">
         <v>237152443.13</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="116" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="10" spans="1:7" s="1" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E10" s="4">
         <v>142369043</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F10" s="4">
         <v>262782527.15000001</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+    <row r="11" spans="1:7" s="1" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E11" s="4">
         <v>129073151</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F11" s="4">
         <v>238568458.66</v>
       </c>
     </row>

--- a/Seguimiento submissions.xlsx
+++ b/Seguimiento submissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luiyi\Dropbox\Lu\Backup\Big data y Machine Learning para Economía Aplicada\Taller-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A45A775-B950-4B79-8080-E384554558F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47AEFAC4-F94E-4765-AD89-602985C73E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{61DA3C93-0847-4C6B-9B33-18547C96FEBD}"/>
+    <workbookView xWindow="19090" yWindow="-7700" windowWidth="38620" windowHeight="21820" xr2:uid="{61DA3C93-0847-4C6B-9B33-18547C96FEBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="72">
   <si>
     <t xml:space="preserve">Archivo </t>
   </si>
@@ -225,6 +225,99 @@
   </si>
   <si>
     <t>Todas + lat y lon + estrato + dtm (889 col)</t>
+  </si>
+  <si>
+    <t>linear_regression</t>
+  </si>
+  <si>
+    <t>Linear Regression</t>
+  </si>
+  <si>
+    <t>Todas numéricas (imputadas con mediana)</t>
+  </si>
+  <si>
+    <t>lm(), log(price) ~ .
+CV normal (k=5): MAE medio = 202,184,245
+Spatial CV (k=5): MAE medio = 195,203,145</t>
+  </si>
+  <si>
+    <t>El modelo lineal muestra una brecha grande entre train y Kaggle (~57%), confirmando dificultad de generalizar a Chapinero. Curioso: Spatial CV (195M) &lt; CV normal (202M), sugiriendo que el modelo generaliza razonablemente en el espacio, aunque con alta varianza entre folds (SD=21M). El fold espacial 3 tuvo MAE excepcionalmente bajo (163M), probablemente capturó zona geográficamente similar a Chapinero.</t>
+  </si>
+  <si>
+    <t>cart</t>
+  </si>
+  <si>
+    <t>CART</t>
+  </si>
+  <si>
+    <t>Todas numéricas (CART maneja NAs internamente)</t>
+  </si>
+  <si>
+    <t>cp = 1e-5, minsplit = 5, maxdepth = 20
+Grid search: 288 combinaciones
+CV normal (k=5): MAE medio = 126,786,640
+Spatial CV (k=5): MAE medio = 160,270,517</t>
+  </si>
+  <si>
+    <t>CV normal eligió árbol profundo (maxdepth=20) y Spatial CV uno más simple (maxdepth=10), con una brecha de ~33M entre ambos — señal de que el árbol profundo sobreajusta a la geografía del train. Variables más importantes: bathrooms, surface_covered, lat, lon. A pesar del buen MAE en CV normal (126M), el Kaggle (246M) refleja dificultad de generalizar a Chapinero.</t>
+  </si>
+  <si>
+    <t>en_ridge</t>
+  </si>
+  <si>
+    <t>Elastic Net (Ridge)</t>
+  </si>
+  <si>
+    <t>Todas numéricas (imputadas con mediana, escaladas)</t>
+  </si>
+  <si>
+    <t>alpha = 0, lambda.min = 0.014196
+cv.glmnet: 10 folds, type.measure = mae</t>
+  </si>
+  <si>
+    <t>Ridge no penaliza a cero ningún coeficiente — todos los predictores quedan activos. MAE Kaggle similar a regresión lineal, lo que sugiere que la regularización L2 no ayuda mucho con el problema de generalización a Chapinero.</t>
+  </si>
+  <si>
+    <t>en_elastic</t>
+  </si>
+  <si>
+    <t>Elastic Net (alpha=0.5)</t>
+  </si>
+  <si>
+    <t>alpha = 0.5, lambda.min = 0.000422
+cv.glmnet: 10 folds, type.measure = mae</t>
+  </si>
+  <si>
+    <t>Combinación L1+L2. Leve mejora sobre Ridge. Lambda muy pequeño indica poca regularización necesaria. Rendimiento casi idéntico a Lasso y Linear Regression.</t>
+  </si>
+  <si>
+    <t>en_lasso</t>
+  </si>
+  <si>
+    <t>Elastic Net (Lasso)</t>
+  </si>
+  <si>
+    <t>alpha = 1, lambda.min = 0.000231
+cv.glmnet: 10 folds, type.measure = mae</t>
+  </si>
+  <si>
+    <t>Lasso es el mejor de los tres Elastic Net. Lambda muy pequeño — selecciona pocas variables pero el efecto es marginal. Los tres modelos lineales (LM, Ridge, Elastic, Lasso) convergen alrededor de 317-320M, confirmando que la limitación es estructural (linealidad) y no de regularización.</t>
+  </si>
+  <si>
+    <t>superlearner</t>
+  </si>
+  <si>
+    <t>SuperLearner (CART + XGBoost + Promedio)</t>
+  </si>
+  <si>
+    <t>Todas numéricas + lat, lon, estrato</t>
+  </si>
+  <si>
+    <t>NNLS weights: CART=0.1497, XGB=0.8503, Promedio=0
+k=5 folds CV normal</t>
+  </si>
+  <si>
+    <t>NNLS asignó peso 0 al promedio simple — la combinación directa CART+XGB es mejor. XGBoost domina con 85% del peso. El SuperLearner mejora al XGBoost solo en CV (104M vs 106M) pero no supera al mejor XGBoost en Kaggle (189M vs 175M). La DTM del texto en xgboost_spatial_cv_dtm sigue siendo clave para generalizar a Chapinero.</t>
   </si>
 </sst>
 </file>
@@ -269,11 +362,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -306,9 +400,13 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Énfasis1" xfId="1" builtinId="29"/>
+    <cellStyle name="Énfasis1 2" xfId="2" xr:uid="{CDDEA17E-7743-432E-B8A4-D282DC987546}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -641,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A70B91BE-477A-4823-BA77-A1BE7105F8DB}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
@@ -902,6 +1000,138 @@
         <v>238568458.66</v>
       </c>
     </row>
+    <row r="12" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="12">
+        <v>202184245</v>
+      </c>
+      <c r="F12" s="12">
+        <v>317386733.64999998</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="12">
+        <v>126786640</v>
+      </c>
+      <c r="F13" s="12">
+        <v>246043324.94</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12">
+        <v>320031734.74000001</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12">
+        <v>317612456.92000002</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12">
+        <v>317587252.63999999</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="12">
+        <v>104739812</v>
+      </c>
+      <c r="F17" s="12">
+        <v>189061480.53999999</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
